--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -637,10 +637,10 @@
         <v>733293</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1412400</v>
+        <v>387292.08</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3558093</v>
+        <v>2532985.08</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -770,10 +770,10 @@
         <v>4039103</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>3869301</v>
+        <v>2844193.08</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>11408924</v>
+        <v>10383816.08</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,11 +53,24 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00D4A017"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00D4A017"/>
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -81,17 +94,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001A6B1A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F5C8B"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="001F5C8B"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -154,55 +177,67 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -570,32 +605,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PRJ13797  —  JMUX REPLACEMENT  |  URB FUNDING REQUEST  |  May 2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>98 Sites Total  —  Phase 1: 31 sites ✅ COMPLETE     Phase 2: 36 sites 🔵 IN PROGRESS     Phase 3: 31 sites ⭕ PENDING</t>
+          <t>98 Sites Total  |  Phase 1: 31 sites ✅ COMPLETE     Phase 2: 36 sites 🔵 IN PROGRESS     Phase 3: 31 sites ⭕ PENDING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>COST CATEGORY / LINE ITEM</t>
+        </is>
+      </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>PHASE 1</t>
@@ -620,14 +659,14 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOTAL PROJECT COST BY PHASE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
+          <t xml:space="preserve">  1.  NOKIA EQUIPMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Nokia Equipment (routers, SFPs, licenses)</t>
+          <t xml:space="preserve">  Routers, Cards &amp; Licenses (confirmed POs Ph1)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -637,432 +676,786 @@
         <v>733293</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>387292.08</v>
+        <v>387292</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2532985.08</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cables &amp; Connectors</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
+        <v>2532985</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SFP+ 10GE CWDM 1491nm Optics — 3HE07161BA (4× Ph3)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOKIA SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1412400</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>733293</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>387292</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>2532985</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2.  CABLES &amp; CONNECTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cable Assemblies, Fiber Jumpers, Connectors</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
         <v>241073</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>279956</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>241073</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>762102</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Engineering — B&amp;M (design, surveys, staging, CSC)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>1161245</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>1428428</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1229914</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>3819587</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Installation — Hawkeye (staging, install, go-live)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CABLES SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>241073</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>279956</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>241073</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>762102</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3.  B&amp;M ENGINEERING — Burns &amp; McDonnell (per SOW RITM3364011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 1 — Staging Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Nokia 7705 SAR card slotting, SFP requirements, staging test plan &amp; execution</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>57300</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>57300</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>57300</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>171900</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 2 — Construction Support Coordinator (CSC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    On-site field engineer during construction &amp; cutover (invoiced monthly)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>368100</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>368100</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>368100</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1104300</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 3 — Substation Site Surveys ($2,390/site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Visual inspection, photos/video, fiber connectivity confirmation per site</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>74090</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>86040</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>160130</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 4 — MPLS Network Node Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    IFR — Issued for Review ($16,695/site)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>517545</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>601020</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>517545</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1636110</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    IFC — Issued for Construction ($5,963/site)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>184853</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>214668</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>184853</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>584374</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — deferred to Phase 3</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>116816</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>116816</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Project Management — $5,500/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    B&amp;M PM fee (Ph1: 1 month | Ph2: 12 months | Ph3: 6 months)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>66000</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>104500</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B&amp;M SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>1207388</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>1393128</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>1277614</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>3878130</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  INSTALLATION — Hawkeye (staging, install, cutover, go-live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Physical installation, rack &amp; stack, cutover, commissioning per site</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
         <v>402793</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C29" s="7" t="n">
         <v>368841</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D29" s="7" t="n">
         <v>744314</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>1515948</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PM, Controls &amp; Scheduler</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>402793</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>368841</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>744314</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>1515948</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C33" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D33" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E33" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Internal Labor (PSEG + Cognizant)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>121360</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>649459</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>116600</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>887419</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C37" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D37" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E37" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PQA, Assessments, NERC-CIP</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>82421</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>436389</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>608810</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C41" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D41" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E41" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOTAL PROJECT EAC</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>3500520</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>4039103</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>2844193.08</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>10383816.08</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PQA SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>79228</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>142737</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>256965</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>3546663</v>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>4003803</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>2891893</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>10442359</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2024 Actuals (already spent — sunk cost)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
         <v>741206</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="n">
+      <c r="C47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="16" t="n">
         <v>741206</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  2025 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B48" s="16" t="n">
         <v>3250000</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="n">
+      <c r="C48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="16" t="n">
         <v>3250000</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="n">
+      <c r="B49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="16" t="n">
         <v>2600000</v>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
+      <c r="D49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="16" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B50" s="18" t="n">
         <v>3991206</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C50" s="18" t="n">
         <v>2600000</v>
       </c>
-      <c r="D18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12" t="n">
+      <c r="D50" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="18" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SCOPE OFFSETS — budget repositioned between phases (nets to $0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  As-Built Drawings deferred to Phase 3</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B53" s="9" t="n">
         <v>-79864</v>
       </c>
-      <c r="C21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="C53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="9" t="n">
         <v>79864</v>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="E53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15" t="n">
+      <c r="B54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9" t="n">
         <v>86000</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D54" s="9" t="n">
         <v>-86000</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="E54" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B55" s="21" t="n">
         <v>-79864</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C55" s="21" t="n">
         <v>86000</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D55" s="21" t="n">
         <v>-6136</v>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="E55" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="20" t="n">
+      <c r="B58" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="24" t="n">
         <v>52500</v>
       </c>
-      <c r="D26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="20" t="n">
+      <c r="D58" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="24" t="n">
         <v>52500</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 × $200/hr)</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="20" t="n">
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="24" t="n">
         <v>240000</v>
       </c>
-      <c r="D27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="20" t="n">
+      <c r="D59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="24" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20" t="n">
+      <c r="B60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="24" t="n">
         <v>259500</v>
       </c>
-      <c r="D28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="20" t="n">
+      <c r="D60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="24" t="n">
         <v>259500</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Materials</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="20" t="n">
+      <c r="B61" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="24" t="n">
         <v>30000</v>
       </c>
-      <c r="D29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="20" t="n">
+      <c r="D61" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="24" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="20" t="n">
+      <c r="B62" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="24" t="n">
         <v>800000</v>
       </c>
-      <c r="D30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="20" t="n">
+      <c r="D62" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="24" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="22" t="n">
+      <c r="B63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="26" t="n">
         <v>1382000</v>
       </c>
-      <c r="D31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="22" t="n">
+      <c r="D63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="26" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E65" s="28" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="18">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -608,7 +608,7 @@
   <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -685,7 +685,7 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SFP+ 10GE CWDM 1491nm Optics — 3HE07161BA (4× Ph3)</t>
+          <t xml:space="preserve">  SFP+ 10GE CWDM 1491nm Optics — 3HE07161BA (4× Ph3, unit price TBD)</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -834,20 +834,20 @@
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Visual inspection, photos/video, fiber connectivity confirmation per site</t>
+          <t xml:space="preserve">    Ph1: 31 sites | Ph2: 36 sites + 31 Ph3 sites pulled in (67 × $2,390) | Ph3: $0</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
         <v>74090</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>86040</v>
+        <v>160130</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>160130</v>
+        <v>234220</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
@@ -898,7 +898,7 @@
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — deferred to Phase 3</t>
+          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — approved, deferred to Ph3</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
@@ -924,7 +924,7 @@
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    B&amp;M PM fee (Ph1: 1 month | Ph2: 12 months | Ph3: 6 months)</t>
+          <t xml:space="preserve">    Ph1: 1 month | Ph2: 12 months | Ph3: 6 months</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
@@ -950,13 +950,13 @@
         <v>1207388</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>1393128</v>
+        <v>1467218</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>1277614</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>3878130</v>
+        <v>3952220</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1139,7 +1139,7 @@
         <v>256965</v>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="28" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
@@ -1149,13 +1149,13 @@
         <v>3546663</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>4003803</v>
+        <v>4077893</v>
       </c>
       <c r="D44" s="13" t="n">
         <v>2891893</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>10442359</v>
+        <v>10516449</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -1251,17 +1251,17 @@
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3</t>
+          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
         </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>-79864</v>
+        <v>-116816</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>79864</v>
+        <v>116816</v>
       </c>
       <c r="E53" s="9" t="n">
         <v>0</v>
@@ -1270,17 +1270,17 @@
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2</t>
+          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
         </is>
       </c>
       <c r="B54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>86000</v>
+        <v>74090</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>-86000</v>
+        <v>-74090</v>
       </c>
       <c r="E54" s="9" t="n">
         <v>0</v>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" s="21" t="n">
-        <v>-79864</v>
+        <v>-116816</v>
       </c>
       <c r="C55" s="21" t="n">
-        <v>86000</v>
+        <v>74090</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>-6136</v>
+        <v>42726</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0</v>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +56,12 @@
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,10 +195,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,7 +246,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -605,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -898,7 +907,7 @@
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — approved, deferred to Ph3</t>
+          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — approved in SOW, deferred to Ph3</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
@@ -924,11 +933,11 @@
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ph1: 1 month | Ph2: 12 months | Ph3: 6 months</t>
+          <t xml:space="preserve">    Ph1: ~6 months ($33,000) | Ph2: 12 months | Ph3: 6 months</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>5500</v>
+        <v>33000</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>66000</v>
@@ -937,524 +946,532 @@
         <v>33000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>104500</v>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Ph1 PM total of $33,000 assumed at 6 months — confirm actual months billed with Chad</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  B&amp;M SUBTOTAL</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>1207388</v>
-      </c>
-      <c r="C26" s="10" t="n">
+      <c r="B27" s="10" t="n">
+        <v>1234888</v>
+      </c>
+      <c r="C27" s="10" t="n">
         <v>1467218</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D27" s="10" t="n">
         <v>1277614</v>
       </c>
-      <c r="E26" s="10" t="n">
-        <v>3952220</v>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="E27" s="10" t="n">
+        <v>3979720</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  INSTALLATION — Hawkeye (staging, install, cutover, go-live)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Physical installation, rack &amp; stack, cutover, commissioning per site</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B30" s="7" t="n">
         <v>402793</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C30" s="7" t="n">
         <v>368841</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D30" s="7" t="n">
         <v>744314</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E30" s="7" t="n">
         <v>1515948</v>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B31" s="10" t="n">
         <v>402793</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C31" s="10" t="n">
         <v>368841</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D31" s="10" t="n">
         <v>744314</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E31" s="10" t="n">
         <v>1515948</v>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B34" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C34" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D34" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E34" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B35" s="10" t="n">
         <v>121360</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C35" s="10" t="n">
         <v>649459</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D35" s="10" t="n">
         <v>116600</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E35" s="10" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B38" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C38" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D38" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E38" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B39" s="10" t="n">
         <v>82421</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C39" s="10" t="n">
         <v>436389</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D39" s="10" t="n">
         <v>90000</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E39" s="10" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B42" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C42" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D42" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E42" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B43" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C43" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D43" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E43" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
-        <v>3546663</v>
-      </c>
-      <c r="C44" s="13" t="n">
+      <c r="B45" s="14" t="n">
+        <v>3574163</v>
+      </c>
+      <c r="C45" s="14" t="n">
         <v>4077893</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D45" s="14" t="n">
         <v>2891893</v>
       </c>
-      <c r="E44" s="13" t="n">
-        <v>10516449</v>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="E45" s="14" t="n">
+        <v>10543949</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>741206</v>
       </c>
-      <c r="C47" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="16" t="n">
+      <c r="C48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
         <v>741206</v>
       </c>
     </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2025 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>3250000</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="16" t="n">
+      <c r="C49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="n">
         <v>3250000</v>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="B50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D49" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="16" t="n">
+      <c r="D50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n">
+      <c r="B51" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C51" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D50" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="18" t="n">
+      <c r="D51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
         </is>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="n">
-        <v>-116816</v>
-      </c>
-      <c r="C53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="9" t="n">
-        <v>116816</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>-116816</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>116816</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="9" t="n">
+      <c r="B55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D55" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E54" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="E55" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n">
+      <c r="B56" s="22" t="n">
         <v>-116816</v>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C56" s="22" t="n">
         <v>74090</v>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D56" s="22" t="n">
         <v>42726</v>
       </c>
-      <c r="E55" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="E56" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
-      <c r="B58" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="24" t="n">
+      <c r="B59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="25" t="n">
         <v>52500</v>
       </c>
-      <c r="D58" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="24" t="n">
+      <c r="D59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="25" t="n">
         <v>52500</v>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
         </is>
       </c>
-      <c r="B59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="24" t="n">
+      <c r="B60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="25" t="n">
         <v>240000</v>
       </c>
-      <c r="D59" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="24" t="n">
+      <c r="D60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="25" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
         </is>
       </c>
-      <c r="B60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="24" t="n">
+      <c r="B61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="25" t="n">
         <v>259500</v>
       </c>
-      <c r="D60" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="24" t="n">
+      <c r="D61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="25" t="n">
         <v>259500</v>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Materials</t>
         </is>
       </c>
-      <c r="B61" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="24" t="n">
+      <c r="B62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="D61" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="24" t="n">
+      <c r="D62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="25" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="23" t="inlineStr">
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B62" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="24" t="n">
+      <c r="B63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D62" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="24" t="n">
+      <c r="D63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="26" t="n">
+      <c r="B64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="26" t="n">
+      <c r="D64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E65" s="28" t="n">
+      <c r="E66" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -614,10 +614,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -978,500 +978,670 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  INSTALLATION — Hawkeye (staging, install, cutover, go-live)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Physical installation, rack &amp; stack, cutover, commissioning per site</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>402793</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>368841</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>744314</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>1515948</v>
+          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (per SOW + Addendum 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Phase 0 — Project Requirements &amp; Planning Complete</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>402793</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>368841</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>744314</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>1515948</v>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>121360</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>649459</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>116600</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>887419</v>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Resource plan, work breakdown structure, delivery schedule, logistics coordination</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 1 — Project Design Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Staging test plan, configuration documentation, card slotting &amp; SFP review with B&amp;M</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 2 — Project Build Complete (Ready for Installation)</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>121360</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>649459</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>116600</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>887419</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>82421</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>436389</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>608810</v>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Equipment assembled, cards installed, powered, burned-in, acceptance tested at staging lab</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 4 — Project Go-Live (Installation &amp; Commissioning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Transport to substation, rack/mount, AC/DC power install, field test, relay cutover support</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 6 — Old Equipment Decommissioned (all phases → Ph3)</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>82421</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>436389</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>608810</v>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n">
-        <v>79228</v>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>142737</v>
-      </c>
-      <c r="D42" s="7" t="n">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Power down old JMUX, dismantle, box and ship to designated location — ALL 98 sites in Ph3</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>200340</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Addendum 1 — Approved Work Directives (WD #1–5, #9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Equipment racks, antenna mast/mounting, subpanel/power wiring, fiber jumpers, inner duct installs</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>68893</v>
+      </c>
+      <c r="C41" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>256965</v>
+      <c r="D41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>103893</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum estimated — actual WDs TBD as Ph2 construction progresses</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>336013</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>302120</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>467460</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>1105593</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>121360</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>649459</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>116600</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>887419</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>121360</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>649459</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>116600</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>887419</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>82421</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>436389</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>608810</v>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>82421</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>436389</v>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>608810</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>79228</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>142737</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>256965</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n">
+      <c r="B55" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C55" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D55" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E55" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
-        <v>3574163</v>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>4077893</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>2891893</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>10543949</v>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="B57" s="14" t="n">
+        <v>3507383</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>4011172</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>2615039</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>10133594</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B60" s="17" t="n">
         <v>741206</v>
       </c>
-      <c r="C48" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="17" t="n">
+      <c r="C60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="17" t="n">
         <v>741206</v>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2025 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B49" s="17" t="n">
+      <c r="B61" s="17" t="n">
         <v>3250000</v>
       </c>
-      <c r="C49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="17" t="n">
+      <c r="C61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="17" t="n">
         <v>3250000</v>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="17" t="n">
+      <c r="B62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="17" t="n">
+      <c r="D62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n">
+      <c r="B63" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C51" s="19" t="n">
+      <c r="C63" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="19" t="n">
+      <c r="D63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n">
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in B&amp;M SOW)</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
         <v>-116816</v>
       </c>
-      <c r="C54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="9" t="n">
+      <c r="C66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="9" t="n">
         <v>116816</v>
       </c>
-      <c r="E54" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="E66" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hawkeye Decommission (M6) deferred to Phase 3 — all 98 sites</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>-66780</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="9" t="n">
+      <c r="B68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D55" s="9" t="n">
+      <c r="D68" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E55" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="E68" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B56" s="22" t="n">
-        <v>-116816</v>
-      </c>
-      <c r="C56" s="22" t="n">
+      <c r="B69" s="22" t="n">
+        <v>-183596</v>
+      </c>
+      <c r="C69" s="22" t="n">
         <v>74090</v>
       </c>
-      <c r="D56" s="22" t="n">
-        <v>42726</v>
-      </c>
-      <c r="E56" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="D69" s="22" t="n">
+        <v>109506</v>
+      </c>
+      <c r="E69" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
-      <c r="B59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="25" t="n">
+      <c r="B72" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="25" t="n">
         <v>52500</v>
       </c>
-      <c r="D59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="25" t="n">
+      <c r="D72" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="25" t="n">
         <v>52500</v>
       </c>
     </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
         </is>
       </c>
-      <c r="B60" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="25" t="n">
+      <c r="B73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="25" t="n">
         <v>240000</v>
       </c>
-      <c r="D60" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="25" t="n">
+      <c r="D73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="25" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
         </is>
       </c>
-      <c r="B61" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="25" t="n">
+      <c r="B74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="25" t="n">
         <v>259500</v>
       </c>
-      <c r="D61" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="25" t="n">
+      <c r="D74" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="25" t="n">
         <v>259500</v>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Materials</t>
         </is>
       </c>
-      <c r="B62" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="25" t="n">
+      <c r="B75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="D62" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="25" t="n">
+      <c r="D75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="25" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="25" t="n">
+      <c r="B76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="25" t="n">
+      <c r="D76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="26" t="inlineStr">
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B64" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="27" t="n">
+      <c r="B77" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D64" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="27" t="n">
+      <c r="D77" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="66" ht="36" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E79" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="26">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A79:D79"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -614,10 +614,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -843,7 +843,7 @@
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ph1: 31 sites | Ph2: 36 sites + 31 Ph3 sites pulled in (67 × $2,390) | Ph3: $0</t>
+          <t xml:space="preserve">    Ph1: 31 sites | Ph2: 36 + 31 Ph3 sites pulled in (67 × $2,390) | Ph3: $0</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -978,21 +978,21 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (per SOW + Addendum 1)</t>
+          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (per SOW MA#8447 + Addendum 1)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Phase 0 — Project Requirements &amp; Planning Complete</t>
+          <t xml:space="preserve">    Phase 0 — Pre-Construction Planning</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Resource plan, work breakdown structure, delivery schedule, logistics coordination</t>
+          <t xml:space="preserve">    IFC document review, RFI coordination with B&amp;M, inventory receipt &amp; BOM prep</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
@@ -1011,14 +1011,14 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 1 — Project Design Complete</t>
+          <t xml:space="preserve">    Milestone 1 — Site Surveys (on-site assessment per substation)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Staging test plan, configuration documentation, card slotting &amp; SFP review with B&amp;M</t>
+          <t xml:space="preserve">    Assess each site: cabinet space, power, fiber path, rack/mounting requirements</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
@@ -1037,14 +1037,14 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 2 — Project Build Complete (Ready for Installation)</t>
+          <t xml:space="preserve">    Milestone 2 — Staging (equipment assembly, burn-in &amp; lab testing)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equipment assembled, cards installed, powered, burned-in, acceptance tested at staging lab</t>
+          <t xml:space="preserve">    Assemble Nokia SAR-8, install cards, load software/config, burn-in &amp; acceptance test</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
@@ -1063,14 +1063,14 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 4 — Project Go-Live (Installation &amp; Commissioning)</t>
+          <t xml:space="preserve">    Milestone 3 — MPLS Installation at Substations</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Transport to substation, rack/mount, AC/DC power install, field test, relay cutover support</t>
+          <t xml:space="preserve">    Rack/mount equipment, AC/DC power install, CAT6/serial/4-wire/fiber cabling, energize &amp; test</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
@@ -1089,560 +1089,587 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 6 — Old Equipment Decommissioned (all phases → Ph3)</t>
+          <t xml:space="preserve">    Milestone 4 — Cutover Support &amp; Go-Live Commissioning</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Power down old JMUX, dismantle, box and ship to designated location — ALL 98 sites in Ph3</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>200340</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Support relay service migration, final commissioning, record docs &amp; checkout checklist</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>200340</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Milestone 6 — Decommission Old JMUX (all phases → Ph3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Power down old JMUX, remove from control house, box &amp; ship — ALL 98 sites in Ph3</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>200340</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>200340</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Addendum 1 — Approved Work Directives (WD #1–5, #9)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Equipment racks, antenna mast/mounting, subpanel/power wiring, fiber jumpers, inner duct installs</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Racks, antenna mast/mounting, subpanel &amp; power wiring, fiber jumpers, inner duct installs</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
         <v>68893</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C43" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="D41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="7" t="n">
+      <c r="D43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>103893</v>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum estimated — actual WDs TBD as Ph2 construction progresses</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 is estimated — update as actual Work Directives are issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n">
-        <v>336013</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>302120</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>467460</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>1105593</v>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="B45" s="10" t="n">
+        <v>402793</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>368900</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>534240</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>1305933</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
+      <c r="B48" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C48" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D48" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E48" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n">
+      <c r="B49" s="10" t="n">
         <v>121360</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C49" s="10" t="n">
         <v>649459</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D49" s="10" t="n">
         <v>116600</v>
       </c>
-      <c r="E47" s="10" t="n">
+      <c r="E49" s="10" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
+      <c r="B52" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C52" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D52" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E52" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n">
+      <c r="B53" s="10" t="n">
         <v>82421</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C53" s="10" t="n">
         <v>436389</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D53" s="10" t="n">
         <v>90000</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E53" s="10" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B56" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C56" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D54" s="7" t="n">
+      <c r="D56" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E54" s="7" t="n">
+      <c r="E56" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n">
+      <c r="B57" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C57" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D57" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E55" s="10" t="n">
+      <c r="E57" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n">
-        <v>3507383</v>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>4011172</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>2615039</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>10133594</v>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="B59" s="14" t="n">
+        <v>3574163</v>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>4077952</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>2681819</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>10333934</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
-      </c>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="n">
-        <v>741206</v>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>741206</v>
-      </c>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2025 Approved Capital Budget</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="C61" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>3250000</v>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>741206</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>741206</v>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2025 Approved Capital Budget</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="17" t="n">
+      <c r="B64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="17" t="n">
+      <c r="D64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n">
+      <c r="B65" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C63" s="19" t="n">
+      <c r="C65" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="19" t="n">
+      <c r="D65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
         </is>
-      </c>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in B&amp;M SOW)</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="n">
-        <v>-116816</v>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="9" t="n">
-        <v>116816</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hawkeye Decommission (M6) deferred to Phase 3 — all 98 sites</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="n">
-        <v>-66780</v>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>66780</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in B&amp;M SOW)</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>-116816</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>116816</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hawkeye Decommission M6 deferred to Phase 3 — all 98 sites</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>-66780</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="9" t="n">
+      <c r="B70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D68" s="9" t="n">
+      <c r="D70" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="E70" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B69" s="22" t="n">
+      <c r="B71" s="22" t="n">
         <v>-183596</v>
       </c>
-      <c r="C69" s="22" t="n">
+      <c r="C71" s="22" t="n">
         <v>74090</v>
       </c>
-      <c r="D69" s="22" t="n">
+      <c r="D71" s="22" t="n">
         <v>109506</v>
       </c>
-      <c r="E69" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="23" t="inlineStr">
+      <c r="E71" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
-      </c>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
-        </is>
-      </c>
-      <c r="B72" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="25" t="n">
-        <v>52500</v>
-      </c>
-      <c r="D72" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="25" t="n">
-        <v>52500</v>
-      </c>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
-        </is>
-      </c>
-      <c r="B73" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="25" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D73" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="25" t="n">
-        <v>240000</v>
       </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
+          <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
       <c r="B74" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="25" t="n">
-        <v>259500</v>
+        <v>52500</v>
       </c>
       <c r="D74" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="25" t="n">
-        <v>259500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAR — Materials</t>
+          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
         </is>
       </c>
       <c r="B75" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="25" t="n">
-        <v>30000</v>
+        <v>240000</v>
       </c>
       <c r="D75" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="25" t="n">
-        <v>30000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
+          <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>259500</v>
+      </c>
+      <c r="D76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="25" t="n">
+        <v>259500</v>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR — Materials</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D77" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="25" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B76" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="25" t="n">
+      <c r="B78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D76" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="25" t="n">
+      <c r="D78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="26" t="inlineStr">
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B77" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="27" t="n">
+      <c r="B79" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D77" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="27" t="n">
+      <c r="D79" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="28" t="inlineStr">
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E79" s="29" t="n">
+      <c r="E81" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A81:D81"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -614,10 +614,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -978,21 +978,21 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (per SOW MA#8447 + Addendum 1)</t>
+          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (SOW MA#8447 + Addendum 1)  |  Base: $333,900  +  Add1: $68,893</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Phase 0 — Pre-Construction Planning</t>
+          <t xml:space="preserve">    Phase 0 — Project Requirements &amp; Planning Complete</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IFC document review, RFI coordination with B&amp;M, inventory receipt &amp; BOM prep</t>
+          <t xml:space="preserve">    WBS, resource plan, cost estimate, delivery schedule; establish staging lab facility</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
@@ -1011,14 +1011,14 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 1 — Site Surveys (on-site assessment per substation)</t>
+          <t xml:space="preserve">    Milestone 1 — Project Design Complete (Pre-Construction)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Assess each site: cabinet space, power, fiber path, rack/mounting requirements</t>
+          <t xml:space="preserve">    Review all IFC drawings, resolve RFIs with B&amp;M, receive &amp; inventory PSEG-supplied equipment, submit BOM</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
@@ -1037,14 +1037,14 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 2 — Staging (equipment assembly, burn-in &amp; lab testing)</t>
+          <t xml:space="preserve">    Milestone 2 — Project Build Complete (Staging &amp; Burn-In)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Assemble Nokia SAR-8, install cards, load software/config, burn-in &amp; acceptance test</t>
+          <t xml:space="preserve">    Assemble Nokia SAR-8 routers &amp; cards, install CWDM/Eltek/RS-232, load software, burn-in &amp; acceptance test at lab</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
@@ -1063,613 +1063,675 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 3 — MPLS Installation at Substations</t>
+          <t xml:space="preserve">    Milestone 3 — Build Quality (95% Acceptance Test Pass Rate)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Rack/mount equipment, AC/DC power install, CAT6/serial/4-wire/fiber cabling, energize &amp; test</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Demonstrate 95%+ pass rate on B&amp;M-approved test cases prior to site deployment (TBD — not yet invoiced)</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: M3 payment amount not defined in SOW ($x,xxx) — confirm value with Hawkeye/Chad</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 4 — Project Ready for Go-Live (MPLS Installation at Substations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Transport to substation; rack/mount; AC/DC power; CAT6/serial/4-wire/fiber cabling; ground bar; energize &amp; test</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
         <v>66780</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C40" s="7" t="n">
         <v>66780</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D40" s="7" t="n">
         <v>66780</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E40" s="7" t="n">
         <v>200340</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Milestone 4 — Cutover Support &amp; Go-Live Commissioning</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Support relay service migration, final commissioning, record docs &amp; checkout checklist</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>66780</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>66780</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>66780</v>
-      </c>
-      <c r="E39" s="7" t="n">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 5 — Post Go-Live Warranty (90-Day Quality Control)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Zero Sev-1 incidents, ≤1 Sev-2, ≤3 Sev-3 defects in 90-day window post cutover (TBD — not yet invoiced)</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: M5 warranty payment not defined in SOW ($x,xxx) — confirm value with Hawkeye/Chad</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Milestone 6 — Old JMUX Decommissioned (all phases → Ph3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Power down old JMUX, remove from control house, box &amp; ship to designated location — ALL 98 sites</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>200340</v>
       </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Milestone 6 — Decommission Old JMUX (all phases → Ph3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Power down old JMUX, remove from control house, box &amp; ship — ALL 98 sites in Ph3</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="9" t="n">
+      <c r="E45" s="9" t="n">
         <v>200340</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>200340</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    Addendum 1 — Approved Work Directives (WD #1–5, #9)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Racks, antenna mast/mounting, subpanel &amp; power wiring, fiber jumpers, inner duct installs</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n">
-        <v>68893</v>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>103893</v>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 is estimated — update as actual Work Directives are issued</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>402793</v>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>368900</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>534240</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>1305933</v>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
-        </is>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD1: Equipment racks for staging  |  WD2: Antenna mast &amp; mounting  |  WD3: Subpanel &amp; power wiring</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>34446</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>17500</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>51946</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">    WD4: Fiber jumpers (Stage 1 &amp; 2 lab)  |  WD5: Melville/Oakwood/Engineering weekly support  |  WD9: Inner duct (9 sites)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>34447</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>17500</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>51947</v>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 is estimated — update as actual Work Directives are issued and approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>336013</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>302120</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>467460</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1105593</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="B53" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C53" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D53" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="E53" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B54" s="10" t="n">
         <v>121360</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C54" s="10" t="n">
         <v>649459</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D54" s="10" t="n">
         <v>116600</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E54" s="10" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B57" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C57" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D57" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E57" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n">
+      <c r="B58" s="10" t="n">
         <v>82421</v>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C58" s="10" t="n">
         <v>436389</v>
       </c>
-      <c r="D53" s="10" t="n">
+      <c r="D58" s="10" t="n">
         <v>90000</v>
       </c>
-      <c r="E53" s="10" t="n">
+      <c r="E58" s="10" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B61" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C61" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D61" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E61" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n">
+      <c r="B62" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C62" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D57" s="10" t="n">
+      <c r="D62" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E57" s="10" t="n">
+      <c r="E62" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B59" s="14" t="n">
-        <v>3574163</v>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>4077952</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>2681819</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>10333934</v>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="B64" s="14" t="n">
+        <v>3507383</v>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>4011172</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>2615039</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>10133594</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B67" s="17" t="n">
         <v>741206</v>
       </c>
-      <c r="C62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="17" t="n">
+      <c r="C67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="17" t="n">
         <v>741206</v>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2025 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B68" s="17" t="n">
         <v>3250000</v>
       </c>
-      <c r="C63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="17" t="n">
+      <c r="C68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="17" t="n">
         <v>3250000</v>
       </c>
     </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="17" t="n">
+      <c r="B69" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="17" t="n">
+      <c r="D69" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="18" t="inlineStr">
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B65" s="19" t="n">
+      <c r="B70" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C65" s="19" t="n">
+      <c r="C70" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="19" t="n">
+      <c r="D70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  As-Built Drawings deferred to Phase 3 (approved in B&amp;M SOW)</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="n">
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B&amp;M As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
         <v>-116816</v>
       </c>
-      <c r="C68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="9" t="n">
+      <c r="C73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="9" t="n">
         <v>116816</v>
       </c>
-      <c r="E68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hawkeye Decommission M6 deferred to Phase 3 — all 98 sites</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="n">
+      <c r="E73" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hawkeye M6 Decommission deferred to Phase 3 — all 98 sites</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
         <v>-66780</v>
       </c>
-      <c r="C69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="9" t="n">
+      <c r="C74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="9" t="n">
         <v>66780</v>
       </c>
-      <c r="E69" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="E74" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="9" t="n">
+      <c r="B75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D70" s="9" t="n">
+      <c r="D75" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E70" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="21" t="inlineStr">
+      <c r="E75" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B71" s="22" t="n">
+      <c r="B76" s="22" t="n">
         <v>-183596</v>
       </c>
-      <c r="C71" s="22" t="n">
+      <c r="C76" s="22" t="n">
         <v>74090</v>
       </c>
-      <c r="D71" s="22" t="n">
+      <c r="D76" s="22" t="n">
         <v>109506</v>
       </c>
-      <c r="E71" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="E76" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
-      <c r="B74" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="25" t="n">
+      <c r="B79" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="25" t="n">
         <v>52500</v>
       </c>
-      <c r="D74" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="25" t="n">
+      <c r="D79" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="25" t="n">
         <v>52500</v>
       </c>
     </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
         </is>
       </c>
-      <c r="B75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="25" t="n">
+      <c r="B80" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="25" t="n">
         <v>240000</v>
       </c>
-      <c r="D75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="25" t="n">
+      <c r="D80" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="25" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
         </is>
       </c>
-      <c r="B76" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="25" t="n">
+      <c r="B81" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="25" t="n">
         <v>259500</v>
       </c>
-      <c r="D76" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="25" t="n">
+      <c r="D81" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="25" t="n">
         <v>259500</v>
       </c>
     </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Materials</t>
         </is>
       </c>
-      <c r="B77" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="25" t="n">
+      <c r="B82" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="D77" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="25" t="n">
+      <c r="D82" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="25" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="24" t="inlineStr">
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="25" t="n">
+      <c r="B83" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D78" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="25" t="n">
+      <c r="D83" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B79" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="27" t="n">
+      <c r="B84" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D79" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="27" t="n">
+      <c r="D84" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="81" ht="36" customHeight="1">
-      <c r="A81" s="28" t="inlineStr">
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E86" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="30">
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A81:D81"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -614,10 +614,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -675,7 +675,7 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Routers, Cards &amp; Licenses (confirmed POs Ph1)</t>
+          <t xml:space="preserve">  Routers, Cards &amp; Licenses (confirmed POs)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -843,7 +843,7 @@
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ph1: 31 sites | Ph2: 36 + 31 Ph3 sites pulled in (67 × $2,390) | Ph3: $0</t>
+          <t xml:space="preserve">    Ph1: 31 sites | Ph2: 36 + 31 Ph3 pulled in = 67 × $2,390 | Ph3: $0</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -907,7 +907,7 @@
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — approved in SOW, deferred to Ph3</t>
+          <t xml:space="preserve">    As-Built Documentation ($1,192/site × 98 sites) — deferred to Ph3</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
@@ -933,7 +933,7 @@
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ph1: ~6 months ($33,000) | Ph2: 12 months | Ph3: 6 months</t>
+          <t xml:space="preserve">    Ph1: ~6 months | Ph2: 12 months | Ph3: 6 months</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
@@ -952,7 +952,7 @@
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ⚠ NOTE: Ph1 PM total of $33,000 assumed at 6 months — confirm actual months billed with Chad</t>
+          <t xml:space="preserve">    ⚠ NOTE: Ph1 PM $33,000 assumed at 6 months — confirm actual months billed with Chad</t>
         </is>
       </c>
     </row>
@@ -978,14 +978,14 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC (SOW MA#8447 + Addendum 1)  |  Base: $333,900  +  Add1: $68,893</t>
+          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC  (SOW MA#8447)  |  Base SOW: $333,900  +  Addendum 1: $68,893</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Phase 0 — Project Requirements &amp; Planning Complete</t>
+          <t xml:space="preserve">    Phase 0 — Project Requirements &amp; Planning</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Review all IFC drawings, resolve RFIs with B&amp;M, receive &amp; inventory PSEG-supplied equipment, submit BOM</t>
+          <t xml:space="preserve">    Review all IFC drawings; resolve RFIs with B&amp;M; receive &amp; inventory PSEG-supplied equipment; submit BOM</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
@@ -1044,7 +1044,7 @@
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Assemble Nokia SAR-8 routers &amp; cards, install CWDM/Eltek/RS-232, load software, burn-in &amp; acceptance test at lab</t>
+          <t xml:space="preserve">    Assemble Nokia SAR-8; install CWDM/Eltek/RS-232 cards; load software &amp; config; burn-in &amp; acceptance test at lab</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
@@ -1070,7 +1070,7 @@
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Demonstrate 95%+ pass rate on B&amp;M-approved test cases prior to site deployment (TBD — not yet invoiced)</t>
+          <t xml:space="preserve">    Demonstrate ≥95% pass rate on B&amp;M-approved test cases prior to site deployment</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
@@ -1089,21 +1089,21 @@
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ⚠ NOTE: M3 payment amount not defined in SOW ($x,xxx) — confirm value with Hawkeye/Chad</t>
+          <t xml:space="preserve">    ⚠ NOTE: M3 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad before next invoice</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 4 — Project Ready for Go-Live (MPLS Installation at Substations)</t>
+          <t xml:space="preserve">    Milestone 4 — MPLS Installation at Substations (Go-Live)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Transport to substation; rack/mount; AC/DC power; CAT6/serial/4-wire/fiber cabling; ground bar; energize &amp; test</t>
+          <t xml:space="preserve">    Transport to substation; rack &amp; mount; AC/DC power; CAT6/serial/4-wire VF/fiber cabling; ground bar; energize &amp; test</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
@@ -1129,7 +1129,7 @@
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Zero Sev-1 incidents, ≤1 Sev-2, ≤3 Sev-3 defects in 90-day window post cutover (TBD — not yet invoiced)</t>
+          <t xml:space="preserve">    Zero Sev-1 incidents, ≤1 Sev-2, ≤3 Sev-3 defects in 90-day window post cutover</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
@@ -1148,21 +1148,21 @@
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ⚠ NOTE: M5 warranty payment not defined in SOW ($x,xxx) — confirm value with Hawkeye/Chad</t>
+          <t xml:space="preserve">    ⚠ NOTE: M5 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad before closeout</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 6 — Old JMUX Decommissioned (all phases → Ph3)</t>
+          <t xml:space="preserve">    Milestone 6 — Old JMUX Decommissioned (all phases consolidated into Ph3)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Power down old JMUX, remove from control house, box &amp; ship to designated location — ALL 98 sites</t>
+          <t xml:space="preserve">    Power down old JMUX; remove from control house; box &amp; ship to designated location — ALL 98 sites</t>
         </is>
       </c>
       <c r="B45" s="9" t="n">
@@ -1181,522 +1181,636 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Addendum 1 — Approved Work Directives (WD #1–5, #9)</t>
+          <t xml:space="preserve">    Addendum 1 — Work Directives #1–5 &amp; #9  (total $68,893 actual)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD1: Equipment racks for staging  |  WD2: Antenna mast &amp; mounting  |  WD3: Subpanel &amp; power wiring</t>
+          <t xml:space="preserve">    WD-01  Equipment racks for expedited programming &amp; burn-in at staging area</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>34446</v>
+        <v>12305</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>51946</v>
+        <v>12305</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD4: Fiber jumpers (Stage 1 &amp; 2 lab)  |  WD5: Melville/Oakwood/Engineering weekly support  |  WD9: Inner duct (9 sites)</t>
+          <t xml:space="preserve">    WD-02  Antenna mast &amp; mounting materials installed at staging area</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>34447</v>
+        <v>9622</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>51947</v>
-      </c>
-    </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 is estimated — update as actual Work Directives are issued and approved</t>
-        </is>
+        <v>9622</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD-03  Subpanel &amp; additional power wiring for staging area operations</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>9444</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>9444</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
-        <v>336013</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>302120</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>467460</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>1105593</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
-        </is>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD-04  Fiber jumpers for Stage 1 &amp; Stage 2 lab programming &amp; testing</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD-05  Weekly operational &amp; engineering support — Melville, Oakwood, Engineering</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>13838</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>13838</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD-09  Inner duct purchase &amp; install — Bagatelle Rd, Pilgrim, Elwood, Syosset, Greenlawn,</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>19532</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>19532</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">             Ruland Rd, East Garden City, Manhasset, Roslyn  (9 sites)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph2 Addendum — Work Directives TBD (estimated)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 estimated — update as individual WDs are approved and invoiced</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>336013</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>302120</v>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>467460</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>1105593</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B59" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C59" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D59" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E59" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n">
+      <c r="B60" s="10" t="n">
         <v>121360</v>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C60" s="10" t="n">
         <v>649459</v>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D60" s="10" t="n">
         <v>116600</v>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E60" s="10" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B63" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C63" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D63" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E63" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B64" s="10" t="n">
         <v>82421</v>
       </c>
-      <c r="C58" s="10" t="n">
+      <c r="C64" s="10" t="n">
         <v>436389</v>
       </c>
-      <c r="D58" s="10" t="n">
+      <c r="D64" s="10" t="n">
         <v>90000</v>
       </c>
-      <c r="E58" s="10" t="n">
+      <c r="E64" s="10" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B67" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C67" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D61" s="7" t="n">
+      <c r="D67" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E67" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B62" s="10" t="n">
+      <c r="B68" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C62" s="10" t="n">
+      <c r="C68" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D68" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E62" s="10" t="n">
+      <c r="E68" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B64" s="14" t="n">
+      <c r="B70" s="14" t="n">
         <v>3507383</v>
       </c>
-      <c r="C64" s="14" t="n">
+      <c r="C70" s="14" t="n">
         <v>4011172</v>
       </c>
-      <c r="D64" s="14" t="n">
+      <c r="D70" s="14" t="n">
         <v>2615039</v>
       </c>
-      <c r="E64" s="14" t="n">
+      <c r="E70" s="14" t="n">
         <v>10133594</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="15" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B73" s="17" t="n">
         <v>741206</v>
       </c>
-      <c r="C67" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="17" t="n">
+      <c r="C73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="17" t="n">
         <v>741206</v>
       </c>
     </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2025 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B74" s="17" t="n">
         <v>3250000</v>
       </c>
-      <c r="C68" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="17" t="n">
+      <c r="C74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="17" t="n">
         <v>3250000</v>
       </c>
     </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="17" t="n">
+      <c r="B75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D69" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="17" t="n">
+      <c r="D75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="18" t="inlineStr">
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B70" s="19" t="n">
+      <c r="B76" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C70" s="19" t="n">
+      <c r="C76" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D70" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="19" t="n">
+      <c r="D76" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B&amp;M As-Built Drawings deferred to Phase 3 (approved in SOW)</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n">
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B&amp;M As-Built Drawings deferred to Phase 3</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
         <v>-116816</v>
       </c>
-      <c r="C73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="9" t="n">
+      <c r="C79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="9" t="n">
         <v>116816</v>
       </c>
-      <c r="E73" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="E79" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Hawkeye M6 Decommission deferred to Phase 3 — all 98 sites</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B80" s="9" t="n">
         <v>-66780</v>
       </c>
-      <c r="C74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="9" t="n">
+      <c r="C80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="9" t="n">
         <v>66780</v>
       </c>
-      <c r="E74" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites total)</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="9" t="n">
+      <c r="E80" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites)</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D81" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E75" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="21" t="inlineStr">
+      <c r="E81" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B76" s="22" t="n">
+      <c r="B82" s="22" t="n">
         <v>-183596</v>
       </c>
-      <c r="C76" s="22" t="n">
+      <c r="C82" s="22" t="n">
         <v>74090</v>
       </c>
-      <c r="D76" s="22" t="n">
+      <c r="D82" s="22" t="n">
         <v>109506</v>
       </c>
-      <c r="E76" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="23" t="inlineStr">
+      <c r="E82" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
-      <c r="B79" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="25" t="n">
+      <c r="B85" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="25" t="n">
         <v>52500</v>
       </c>
-      <c r="D79" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="25" t="n">
+      <c r="D85" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="25" t="n">
         <v>52500</v>
       </c>
     </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
         </is>
       </c>
-      <c r="B80" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="25" t="n">
+      <c r="B86" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="25" t="n">
         <v>240000</v>
       </c>
-      <c r="D80" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="25" t="n">
+      <c r="D86" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="25" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="24" t="inlineStr">
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
         </is>
       </c>
-      <c r="B81" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="25" t="n">
+      <c r="B87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="25" t="n">
         <v>259500</v>
       </c>
-      <c r="D81" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="25" t="n">
+      <c r="D87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="25" t="n">
         <v>259500</v>
       </c>
     </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="24" t="inlineStr">
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PAR — Materials</t>
         </is>
       </c>
-      <c r="B82" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="25" t="n">
+      <c r="B88" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="D82" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="25" t="n">
+      <c r="D88" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="25" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="24" t="inlineStr">
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="25" t="n">
+      <c r="B89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="25" t="n">
+      <c r="D89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="26" t="inlineStr">
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B84" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="27" t="n">
+      <c r="B90" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D84" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="27" t="n">
+      <c r="D90" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E86" s="29" t="n">
+      <c r="E92" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
@@ -1706,31 +1820,31 @@
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -978,7 +978,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC  (SOW MA#8447)  |  Base SOW: $333,900  +  Addendum 1: $68,893</t>
+          <t xml:space="preserve">  4.  INSTALLATION — Elecnor Hawkeye LLC  (SOW MA#8447)  |  Base: $333,900  +  Add.1: $68,893</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Assemble Nokia SAR-8; install CWDM/Eltek/RS-232 cards; load software &amp; config; burn-in &amp; acceptance test at lab</t>
+          <t xml:space="preserve">    Assemble Nokia SAR-8; install CWDM/Eltek/RS-232 cards; load software &amp; config; burn-in &amp; acceptance test</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
@@ -1089,7 +1089,7 @@
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ⚠ NOTE: M3 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad before next invoice</t>
+          <t xml:space="preserve">    ⚠ NOTE: M3 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1148,21 @@
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ⚠ NOTE: M5 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad before closeout</t>
+          <t xml:space="preserve">    ⚠ NOTE: M5 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Milestone 6 — Old JMUX Decommissioned (all phases consolidated into Ph3)</t>
+          <t xml:space="preserve">    Milestone 6 — Old JMUX Decommissioned  ★  ALL PHASES → Ph3</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Power down old JMUX; remove from control house; box &amp; ship to designated location — ALL 98 sites</t>
+          <t xml:space="preserve">    Ph1 decom (31 sites) — deferred: Hawkeye returns after parallel run to power down, remove &amp; ship</t>
         </is>
       </c>
       <c r="B45" s="9" t="n">
@@ -1172,65 +1172,65 @@
         <v>0</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>200340</v>
+        <v>66780</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>200340</v>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Addendum 1 — Work Directives #1–5 &amp; #9  (total $68,893 actual)</t>
-        </is>
+        <v>66780</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph2 decom (36 sites) — deferred: same process, executed during Ph3 window</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>66780</v>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WD-01  Equipment racks for expedited programming &amp; burn-in at staging area</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>12305</v>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>12305</v>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WD-02  Antenna mast &amp; mounting materials installed at staging area</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>9622</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>9622</v>
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph3 decom (31 sites) — concurrent with Ph3 installation &amp; cutover</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>66780</v>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Addendum 1 — Work Directives #1–5 &amp; #9  (actual $68,893)</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD-03  Subpanel &amp; additional power wiring for staging area operations</t>
+          <t xml:space="preserve">    WD-01  Equipment racks for expedited programming &amp; burn-in at staging area</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>9444</v>
+        <v>12305</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>0</v>
@@ -1239,17 +1239,17 @@
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>9444</v>
+        <v>12305</v>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD-04  Fiber jumpers for Stage 1 &amp; Stage 2 lab programming &amp; testing</t>
+          <t xml:space="preserve">    WD-02  Antenna mast &amp; mounting materials installed at staging area</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>4152</v>
+        <v>9622</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>0</v>
@@ -1258,17 +1258,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>4152</v>
+        <v>9622</v>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD-05  Weekly operational &amp; engineering support — Melville, Oakwood, Engineering</t>
+          <t xml:space="preserve">    WD-03  Subpanel &amp; additional power wiring for staging area operations</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>13838</v>
+        <v>9444</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>0</v>
@@ -1277,17 +1277,17 @@
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>13838</v>
+        <v>9444</v>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WD-09  Inner duct purchase &amp; install — Bagatelle Rd, Pilgrim, Elwood, Syosset, Greenlawn,</t>
+          <t xml:space="preserve">    WD-04  Fiber jumpers for Stage 1 &amp; Stage 2 lab programming &amp; testing</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>19532</v>
+        <v>4152</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>0</v>
@@ -1296,521 +1296,578 @@
         <v>0</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>19532</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">    WD-05  Weekly operational &amp; engineering support — Melville, Oakwood, Engineering</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>13838</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>13838</v>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WD-09  Inner duct purchase &amp; install — Bagatelle Rd, Pilgrim, Elwood, Syosset,</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>19532</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>19532</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">             Ruland Rd, East Garden City, Manhasset, Roslyn  (9 sites)</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="B55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Ph2 Addendum — Work Directives TBD (estimated)</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="9" t="n">
+      <c r="B56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="9" t="n">
         <v>35000</v>
       </c>
-      <c r="D54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="9" t="n">
+      <c r="D56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9" t="n">
         <v>35000</v>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 estimated — update as individual WDs are approved and invoiced</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAWKEYE SUBTOTAL</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n">
+      <c r="B58" s="10" t="n">
         <v>336013</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C58" s="10" t="n">
         <v>302120</v>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D58" s="10" t="n">
         <v>467460</v>
       </c>
-      <c r="E56" s="10" t="n">
+      <c r="E58" s="10" t="n">
         <v>1105593</v>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  PM, CONTROLS &amp; SCHEDULER</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Project Management, Controls, Scheduling resources</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B61" s="7" t="n">
         <v>121360</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C61" s="7" t="n">
         <v>649459</v>
       </c>
-      <c r="D59" s="7" t="n">
+      <c r="D61" s="7" t="n">
         <v>116600</v>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E61" s="7" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PM/CONTROLS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B60" s="10" t="n">
+      <c r="B62" s="10" t="n">
         <v>121360</v>
       </c>
-      <c r="C60" s="10" t="n">
+      <c r="C62" s="10" t="n">
         <v>649459</v>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D62" s="10" t="n">
         <v>116600</v>
       </c>
-      <c r="E60" s="10" t="n">
+      <c r="E62" s="10" t="n">
         <v>887419</v>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  INTERNAL LABOR (PSEG + Cognizant)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  PSEG internal resources, Cognizant support</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B65" s="7" t="n">
         <v>82421</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C65" s="7" t="n">
         <v>436389</v>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D65" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E65" s="7" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  INTERNAL LABOR SUBTOTAL</t>
         </is>
       </c>
-      <c r="B64" s="10" t="n">
+      <c r="B66" s="10" t="n">
         <v>82421</v>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C66" s="10" t="n">
         <v>436389</v>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D66" s="10" t="n">
         <v>90000</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E66" s="10" t="n">
         <v>608810</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  PQA, ASSESSMENTS &amp; NERC-CIP</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Power Quality Assessments, NERC-CIP compliance</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B69" s="7" t="n">
         <v>79228</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C69" s="7" t="n">
         <v>142737</v>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D69" s="7" t="n">
         <v>35000</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E69" s="7" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  PQA SUBTOTAL</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n">
+      <c r="B70" s="10" t="n">
         <v>79228</v>
       </c>
-      <c r="C68" s="10" t="n">
+      <c r="C70" s="10" t="n">
         <v>142737</v>
       </c>
-      <c r="D68" s="10" t="n">
+      <c r="D70" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="E68" s="10" t="n">
+      <c r="E70" s="10" t="n">
         <v>256965</v>
       </c>
     </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ★  TOTAL PROJECT EAC</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
+      <c r="B72" s="14" t="n">
         <v>3507383</v>
       </c>
-      <c r="C70" s="14" t="n">
+      <c r="C72" s="14" t="n">
         <v>4011172</v>
       </c>
-      <c r="D70" s="14" t="n">
+      <c r="D72" s="14" t="n">
         <v>2615039</v>
       </c>
-      <c r="E70" s="14" t="n">
+      <c r="E72" s="14" t="n">
         <v>10133594</v>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  LESS: APPROVED BUDGET (already authorized)</t>
         </is>
-      </c>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>741206</v>
-      </c>
-      <c r="C73" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>741206</v>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2025 Approved Capital Budget</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="C74" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>3250000</v>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2024 Actuals (sunk cost)</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="n">
+        <v>741206</v>
+      </c>
+      <c r="C75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>741206</v>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2025 Approved Capital Budget</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="C76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  2026 Approved Capital Budget</t>
         </is>
       </c>
-      <c r="B75" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="17" t="n">
+      <c r="B77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="D75" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="17" t="n">
+      <c r="D77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="17" t="n">
         <v>2600000</v>
       </c>
     </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="18" t="inlineStr">
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL APPROVED</t>
         </is>
       </c>
-      <c r="B76" s="19" t="n">
+      <c r="B78" s="19" t="n">
         <v>3991206</v>
       </c>
-      <c r="C76" s="19" t="n">
+      <c r="C78" s="19" t="n">
         <v>2600000</v>
       </c>
-      <c r="D76" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="19" t="n">
+      <c r="D78" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="19" t="n">
         <v>6591206</v>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SCOPE OFFSETS — repositioned between phases (net $0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B&amp;M As-Built Drawings deferred to Phase 3</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>-116816</v>
-      </c>
-      <c r="C79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>116816</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hawkeye M6 Decommission deferred to Phase 3 — all 98 sites</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>-66780</v>
-      </c>
-      <c r="C80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>66780</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0</v>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SCOPE OFFSETS — cost repositioned between phases (net $0 impact)</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (67 sites)</t>
+          <t xml:space="preserve">  B&amp;M As-Built Documentation — deferred from Ph1/Ph2 to Ph3</t>
         </is>
       </c>
       <c r="B81" s="9" t="n">
-        <v>0</v>
+        <v>-116816</v>
       </c>
       <c r="C81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>116816</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hawkeye M6 Decom Ph1 (31 sites) — deferred to Ph3</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>-66780</v>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hawkeye M6 Decom Ph2 (36 sites) — deferred to Ph3</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>-66780</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>66780</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Phase 3 Site Surveys pulled into Phase 2 (31 sites × $2,390)</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="9" t="n">
         <v>74090</v>
       </c>
-      <c r="D81" s="9" t="n">
+      <c r="D84" s="9" t="n">
         <v>-74090</v>
       </c>
-      <c r="E81" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
+      <c r="E84" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  NET OFFSET IMPACT</t>
         </is>
       </c>
-      <c r="B82" s="22" t="n">
+      <c r="B85" s="22" t="n">
         <v>-183596</v>
       </c>
-      <c r="C82" s="22" t="n">
-        <v>74090</v>
-      </c>
-      <c r="D82" s="22" t="n">
-        <v>109506</v>
-      </c>
-      <c r="E82" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="23" t="inlineStr">
+      <c r="C85" s="22" t="n">
+        <v>7310</v>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>176286</v>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PLUS: NEW SCOPE  ★  PCR REQUIRED</t>
         </is>
-      </c>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
-        </is>
-      </c>
-      <c r="B85" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="25" t="n">
-        <v>52500</v>
-      </c>
-      <c r="D85" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="25" t="n">
-        <v>52500</v>
-      </c>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
-        </is>
-      </c>
-      <c r="B86" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="25" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D86" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="25" t="n">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
-        </is>
-      </c>
-      <c r="B87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="25" t="n">
-        <v>259500</v>
-      </c>
-      <c r="D87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="25" t="n">
-        <v>259500</v>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAR — Materials</t>
+          <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
         </is>
       </c>
       <c r="B88" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="25" t="n">
-        <v>30000</v>
+        <v>52500</v>
       </c>
       <c r="D88" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E88" s="25" t="n">
-        <v>30000</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
         <is>
+          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="25" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="25" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="25" t="n">
+        <v>259500</v>
+      </c>
+      <c r="D90" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="25" t="n">
+        <v>259500</v>
+      </c>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR — Materials</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D91" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
         </is>
       </c>
-      <c r="B89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="25" t="n">
+      <c r="B92" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="25" t="n">
         <v>800000</v>
       </c>
-      <c r="D89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="25" t="n">
+      <c r="D92" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="25" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="26" t="inlineStr">
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOTAL NEW SCOPE</t>
         </is>
       </c>
-      <c r="B90" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="27" t="n">
+      <c r="B93" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="27" t="n">
         <v>1382000</v>
       </c>
-      <c r="D90" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="27" t="n">
+      <c r="D93" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="27" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="A92" s="28" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E92" s="29" t="n">
+      <c r="E95" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
@@ -1819,32 +1876,32 @@
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A95:D95"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PRJ13797_JMUX_URB_Simple.xlsx
+++ b/PRJ13797_JMUX_URB_Simple.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +75,20 @@
       <color rgb="00D4A017"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -133,8 +145,13 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E06666"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -156,11 +173,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -247,6 +308,26 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -729,6 +810,7 @@
         <v>2532985</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -774,6 +856,7 @@
         <v>762102</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -955,6 +1038,10 @@
           <t xml:space="preserve">    ⚠ NOTE: Ph1 PM $33,000 assumed at 6 months — confirm actual months billed with Chad</t>
         </is>
       </c>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="31" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -975,6 +1062,7 @@
         <v>3979720</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -1092,6 +1180,10 @@
           <t xml:space="preserve">    ⚠ NOTE: M3 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad</t>
         </is>
       </c>
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="31" t="n"/>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -1151,6 +1243,10 @@
           <t xml:space="preserve">    ⚠ NOTE: M5 amount listed as $x,xxx in SOW — confirm dollar value with Hawkeye / Chad</t>
         </is>
       </c>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="31" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -1381,6 +1477,10 @@
           <t xml:space="preserve">    ⚠ NOTE: Ph2 Addendum $35,000 estimated — update as individual WDs are approved and invoiced</t>
         </is>
       </c>
+      <c r="B57" s="30" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="30" t="n"/>
+      <c r="E57" s="31" t="n"/>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -1401,6 +1501,7 @@
         <v>1105593</v>
       </c>
     </row>
+    <row r="59"/>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
@@ -1446,6 +1547,7 @@
         <v>887419</v>
       </c>
     </row>
+    <row r="63"/>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
@@ -1491,6 +1593,7 @@
         <v>608810</v>
       </c>
     </row>
+    <row r="67"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -1536,6 +1639,7 @@
         <v>256965</v>
       </c>
     </row>
+    <row r="71"/>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="13" t="inlineStr">
         <is>
@@ -1555,6 +1659,7 @@
         <v>10133594</v>
       </c>
     </row>
+    <row r="73"/>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
         <is>
@@ -1638,6 +1743,7 @@
         <v>6591206</v>
       </c>
     </row>
+    <row r="79"/>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="20" t="inlineStr">
         <is>
@@ -1740,6 +1846,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86"/>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
@@ -1747,132 +1854,414 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Equipment (Iniven RC-30 × 6 sites)</t>
-        </is>
-      </c>
-      <c r="B88" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="25" t="n">
-        <v>52500</v>
-      </c>
-      <c r="D88" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="25" t="n">
-        <v>52500</v>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAR Circuit Migration — 6 High-Impact Substations  |  Northport, Hicksville (5HK), Melville, Lindenhurst (7Z), Far Rockaway (2H), Hewlett (2R)</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR — Engineering (200 hrs × 6 sites × $200/hr)</t>
-        </is>
-      </c>
-      <c r="B89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="25" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D89" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="25" t="n">
-        <v>240000</v>
+      <c r="A89" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAR — Protection Engineering Design  (Chokrapani / Locke / Samir team)</t>
+        </is>
+      </c>
+      <c r="B89" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAR — Installation (~1,298 hrs × $200/hr)</t>
+          <t xml:space="preserve">      Site 1  Northport           200 hrs × $200/hr</t>
         </is>
       </c>
       <c r="B90" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="25" t="n">
-        <v>259500</v>
+        <v>40000</v>
       </c>
       <c r="D90" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E90" s="25" t="n">
-        <v>259500</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAR — Materials</t>
+          <t xml:space="preserve">      Site 2  Hicksville (5HK)    200 hrs × $200/hr</t>
         </is>
       </c>
       <c r="B91" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="25" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D91" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E91" s="25" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Phase 3 Design Acceleration into Phase 2</t>
+          <t xml:space="preserve">      Site 3  Melville            200 hrs × $200/hr</t>
         </is>
       </c>
       <c r="B92" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D92" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="25" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Site 4  Lindenhurst (7Z)    200 hrs × $200/hr</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D93" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="25" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Site 5  Far Rockaway (2H)   200 hrs × $200/hr</t>
+        </is>
+      </c>
+      <c r="B94" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D94" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="25" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Site 6  Hewlett (2R)        200 hrs × $200/hr</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D95" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="25" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Engineering Subtotal  (6 sites × 200 hrs × $200/hr)</t>
+        </is>
+      </c>
+      <c r="B96" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D96" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="35" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Actual monthly spend ~$10K vs $30K forecast — total may revise below $240K pending bench test results (Locke to confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAR — Equipment Procurement  (Iniven RC-30 devices)</t>
+        </is>
+      </c>
+      <c r="B98" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      PO SCL2595 — Iniven RC-30 × 6 units  (ordered for Site 1, remaining 5 pending bench test)</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="25" t="n">
+        <v>52500</v>
+      </c>
+      <c r="D99" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="25" t="n">
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Site 1 device delivery expected ~May 25-28. Remaining 5 units to be ordered after bench test passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAR — Installation, Configuration &amp; Cutover  (Steven Bradley / Johnny relay team)</t>
+        </is>
+      </c>
+      <c r="B101" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Relay team labor  ~1,298 hrs × $200/hr  (per Steven Bradley cost estimate)</t>
+        </is>
+      </c>
+      <c r="B102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="25" t="n">
+        <v>259500</v>
+      </c>
+      <c r="D102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="25" t="n">
+        <v>259500</v>
+      </c>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Materials — cables, connectors, ancillary items</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="25" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR SUBTOTAL  (Eng $240K + Equipment $52.5K + Install $259.5K + Materials $30K)</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="27" t="n">
+        <v>582000</v>
+      </c>
+      <c r="D104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="27" t="n">
+        <v>582000</v>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Phase 3 Work Accelerated into Phase 2  (schedule recovery — 5-month impact mitigation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph3 Site Surveys pulled into Ph2  (31 sites × $2,390 = $74,090 via B&amp;M)</t>
+        </is>
+      </c>
+      <c r="B106" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="25" t="n">
+        <v>74090</v>
+      </c>
+      <c r="D106" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="25" t="n">
+        <v>74090</v>
+      </c>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph3 MPLS Detail Design (IFR/IFC) accelerated into Ph2  (31 sites via B&amp;M)</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="25" t="n">
+        <v>517545</v>
+      </c>
+      <c r="D107" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="25" t="n">
+        <v>517545</v>
+      </c>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ph3 Relay/RTU engineering support pulled forward</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="25" t="n">
+        <v>208365</v>
+      </c>
+      <c r="D108" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="25" t="n">
+        <v>208365</v>
+      </c>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⚠ NOTE: Acceleration recovers 5-month schedule slip caused by PAR discovery — without this, project end slips to May 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PHASE 3 ACCELERATION SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="27" t="n">
         <v>800000</v>
       </c>
-      <c r="D92" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="25" t="n">
+      <c r="D110" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="27" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOTAL NEW SCOPE</t>
-        </is>
-      </c>
-      <c r="B93" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="27" t="n">
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★  TOTAL NEW SCOPE (PCR)</t>
+        </is>
+      </c>
+      <c r="B111" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="37" t="n">
         <v>1382000</v>
       </c>
-      <c r="D93" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="27" t="n">
+      <c r="D111" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="37" t="n">
         <v>1382000</v>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="A95" s="28" t="inlineStr">
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★★  NET NEW FUNDING REQUIRED — URB ASK</t>
         </is>
       </c>
-      <c r="E95" s="29" t="n">
+      <c r="E113" s="29" t="n">
         <v>1400000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="36">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
@@ -1882,24 +2271,30 @@
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A113:D113"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A9:E9"/>
